--- a/p6_deployment/data/germany/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,8 +702,15 @@
         <v>45520.65625</v>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>19500</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>tbC3EcQn</t>
@@ -916,8 +923,15 @@
         <v>45521.4375</v>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4990</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Q1yNyI5t</t>
@@ -1075,8 +1089,15 @@
         <v>45521.4375</v>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>16667</v>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>88Xgj1Y5</t>
@@ -1126,8 +1147,15 @@
         <v>45521.4375</v>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>8000</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>lKLJUxeT</t>
@@ -1557,8 +1585,15 @@
         <v>45522.4375</v>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>10000</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>E3xs5mIe</t>
@@ -1771,8 +1806,15 @@
         <v>45522.54166666666</v>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>10059</v>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>hjNlCFPB</t>
@@ -1921,7 +1963,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1931,50 +1973,282 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>dfb pokal</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>22450</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6g44VD52</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>59</v>
+      </c>
+      <c r="K28" t="n">
+        <v>593</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>20500</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>YJURlaIO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>59</v>
+      </c>
+      <c r="K29" t="n">
+        <v>593</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>9500</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>p8wBsqZt</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>59</v>
+      </c>
+      <c r="K30" t="n">
+        <v>593</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>23325</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>59</v>
+      </c>
+      <c r="K31" t="n">
+        <v>593</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">bayarena
   leverkusen </t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="G32" t="n">
         <v>30210</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>59</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="J32" t="n">
+        <v>59</v>
+      </c>
+      <c r="K32" t="n">
         <v>594</v>
       </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
         <v>2024</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
